--- a/public/results/2025/2025 Weekly Stats - Week 5.xlsx
+++ b/public/results/2025/2025 Weekly Stats - Week 5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mthutter/CODE/golf-league-site/public/results/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3D547C-1A90-4C44-A9D7-6D8E7D9E75D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E17EB9CD-485B-7A42-87F4-4FB9B964E0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5780" yWindow="2560" windowWidth="29860" windowHeight="16420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1225,7 +1225,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1546,9 +1546,6 @@
     <xf numFmtId="1" fontId="23" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1570,14 +1567,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1586,6 +1577,75 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1610,18 +1670,6 @@
     <xf numFmtId="1" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="18" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1637,63 +1685,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1703,7 +1694,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2296,23 +2287,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
@@ -2326,23 +2317,23 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A2" s="133" t="s">
+      <c r="A2" s="130" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -4315,111 +4306,111 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" s="1" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="154" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="140" t="s">
+      <c r="B1" s="155"/>
+      <c r="C1" s="160" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="142" t="s">
+      <c r="D1" s="144" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="143"/>
-      <c r="F1" s="142" t="s">
+      <c r="E1" s="145"/>
+      <c r="F1" s="144" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="143"/>
-      <c r="H1" s="142" t="s">
+      <c r="G1" s="145"/>
+      <c r="H1" s="144" t="s">
         <v>82</v>
       </c>
-      <c r="I1" s="143"/>
-      <c r="J1" s="142" t="s">
+      <c r="I1" s="145"/>
+      <c r="J1" s="144" t="s">
         <v>84</v>
       </c>
-      <c r="K1" s="143"/>
-      <c r="L1" s="142" t="s">
+      <c r="K1" s="145"/>
+      <c r="L1" s="144" t="s">
         <v>87</v>
       </c>
-      <c r="M1" s="143"/>
-      <c r="N1" s="168" t="s">
+      <c r="M1" s="145"/>
+      <c r="N1" s="142" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="157" t="s">
+      <c r="O1" s="131" t="s">
         <v>45</v>
       </c>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
-      <c r="R1" s="158"/>
-      <c r="S1" s="159"/>
-      <c r="T1" s="146" t="s">
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
+      <c r="R1" s="132"/>
+      <c r="S1" s="133"/>
+      <c r="T1" s="162" t="s">
         <v>46</v>
       </c>
-      <c r="U1" s="147"/>
-      <c r="V1" s="147"/>
-      <c r="W1" s="147"/>
-      <c r="X1" s="148"/>
+      <c r="U1" s="163"/>
+      <c r="V1" s="163"/>
+      <c r="W1" s="163"/>
+      <c r="X1" s="164"/>
     </row>
     <row r="2" spans="1:24" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="136"/>
-      <c r="B2" s="137"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="144">
+      <c r="A2" s="156"/>
+      <c r="B2" s="157"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="146">
         <v>45782</v>
       </c>
-      <c r="E2" s="145"/>
-      <c r="F2" s="144">
+      <c r="E2" s="147"/>
+      <c r="F2" s="146">
         <v>45789</v>
       </c>
-      <c r="G2" s="145"/>
-      <c r="H2" s="144">
+      <c r="G2" s="147"/>
+      <c r="H2" s="146">
         <v>45796</v>
       </c>
-      <c r="I2" s="145"/>
-      <c r="J2" s="144">
+      <c r="I2" s="147"/>
+      <c r="J2" s="146">
         <v>45803</v>
       </c>
-      <c r="K2" s="145"/>
-      <c r="L2" s="144">
+      <c r="K2" s="147"/>
+      <c r="L2" s="146">
         <v>45810</v>
       </c>
-      <c r="M2" s="145"/>
-      <c r="N2" s="169"/>
-      <c r="O2" s="160" t="s">
+      <c r="M2" s="147"/>
+      <c r="N2" s="143"/>
+      <c r="O2" s="134" t="s">
         <v>41</v>
       </c>
-      <c r="P2" s="162" t="s">
+      <c r="P2" s="136" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="166" t="s">
+      <c r="Q2" s="140" t="s">
         <v>79</v>
       </c>
-      <c r="R2" s="160" t="s">
+      <c r="R2" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="S2" s="164" t="s">
+      <c r="S2" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="T2" s="149" t="s">
+      <c r="T2" s="165" t="s">
         <v>41</v>
       </c>
-      <c r="U2" s="149" t="s">
+      <c r="U2" s="165" t="s">
         <v>44</v>
       </c>
-      <c r="V2" s="149" t="s">
+      <c r="V2" s="165" t="s">
         <v>79</v>
       </c>
-      <c r="W2" s="149" t="s">
+      <c r="W2" s="165" t="s">
         <v>13</v>
       </c>
-      <c r="X2" s="149" t="s">
+      <c r="X2" s="165" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:24" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="138"/>
-      <c r="B3" s="139"/>
-      <c r="C3" s="141"/>
+      <c r="A3" s="158"/>
+      <c r="B3" s="159"/>
+      <c r="C3" s="161"/>
       <c r="D3" s="38" t="s">
         <v>4</v>
       </c>
@@ -4450,17 +4441,17 @@
       <c r="M3" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="N3" s="169"/>
-      <c r="O3" s="161"/>
-      <c r="P3" s="163"/>
-      <c r="Q3" s="167"/>
-      <c r="R3" s="161"/>
-      <c r="S3" s="165"/>
-      <c r="T3" s="150"/>
-      <c r="U3" s="150"/>
-      <c r="V3" s="150"/>
-      <c r="W3" s="150"/>
-      <c r="X3" s="150"/>
+      <c r="N3" s="143"/>
+      <c r="O3" s="135"/>
+      <c r="P3" s="137"/>
+      <c r="Q3" s="141"/>
+      <c r="R3" s="135"/>
+      <c r="S3" s="139"/>
+      <c r="T3" s="166"/>
+      <c r="U3" s="166"/>
+      <c r="V3" s="166"/>
+      <c r="W3" s="166"/>
+      <c r="X3" s="166"/>
     </row>
     <row r="4" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="39" t="s">
@@ -4472,23 +4463,25 @@
       <c r="C4" s="41">
         <v>22</v>
       </c>
-      <c r="D4" s="128"/>
-      <c r="E4" s="152"/>
+      <c r="D4" s="148" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="149"/>
       <c r="F4" s="68">
         <v>53</v>
       </c>
       <c r="G4" s="72">
         <v>23</v>
       </c>
-      <c r="H4" s="151" t="s">
+      <c r="H4" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I4" s="152"/>
+      <c r="I4" s="149"/>
       <c r="J4" s="68"/>
       <c r="K4" s="72"/>
       <c r="L4" s="68"/>
       <c r="M4" s="72"/>
-      <c r="N4" s="121">
+      <c r="N4" s="120">
         <f>F4+J4+L4</f>
         <v>53</v>
       </c>
@@ -4496,7 +4489,7 @@
         <f>COUNTIF(D4:L4,"&gt;30")</f>
         <v>1</v>
       </c>
-      <c r="P4" s="124"/>
+      <c r="P4" s="123"/>
       <c r="Q4" s="72"/>
       <c r="R4" s="60">
         <f>SUMIF(G4:M4, "&lt;30")+P4+Q4</f>
@@ -4524,18 +4517,16 @@
       <c r="C5" s="44">
         <v>15</v>
       </c>
-      <c r="D5" s="129" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" s="154"/>
+      <c r="D5" s="150"/>
+      <c r="E5" s="151"/>
       <c r="F5" s="45">
         <v>42</v>
       </c>
       <c r="G5" s="73">
         <v>27</v>
       </c>
-      <c r="H5" s="153"/>
-      <c r="I5" s="154"/>
+      <c r="H5" s="150"/>
+      <c r="I5" s="151"/>
       <c r="J5" s="45"/>
       <c r="K5" s="73"/>
       <c r="L5" s="45">
@@ -4544,7 +4535,7 @@
       <c r="M5" s="73">
         <v>15</v>
       </c>
-      <c r="N5" s="122">
+      <c r="N5" s="121">
         <f>F5+J5+L5</f>
         <v>96</v>
       </c>
@@ -4552,7 +4543,7 @@
         <f>COUNTIF(D5:L5,"&gt;30")</f>
         <v>2</v>
       </c>
-      <c r="P5" s="125"/>
+      <c r="P5" s="124"/>
       <c r="Q5" s="73"/>
       <c r="R5" s="61">
         <f>SUMIF(G5:M5, "&lt;30")+P5+Q5</f>
@@ -4578,16 +4569,16 @@
       <c r="C6" s="44">
         <v>13</v>
       </c>
-      <c r="D6" s="129"/>
-      <c r="E6" s="154"/>
+      <c r="D6" s="150"/>
+      <c r="E6" s="151"/>
       <c r="F6" s="76">
         <v>42</v>
       </c>
       <c r="G6" s="73">
         <v>25</v>
       </c>
-      <c r="H6" s="153"/>
-      <c r="I6" s="154"/>
+      <c r="H6" s="150"/>
+      <c r="I6" s="151"/>
       <c r="J6" s="76"/>
       <c r="K6" s="73"/>
       <c r="L6" s="119">
@@ -4596,7 +4587,7 @@
       <c r="M6" s="73">
         <v>16</v>
       </c>
-      <c r="N6" s="122">
+      <c r="N6" s="121">
         <f>F6+J6+L6</f>
         <v>93</v>
       </c>
@@ -4604,7 +4595,7 @@
         <f>COUNTIF(D6:L6,"&gt;30")</f>
         <v>2</v>
       </c>
-      <c r="P6" s="125">
+      <c r="P6" s="124">
         <v>1</v>
       </c>
       <c r="Q6" s="73"/>
@@ -4632,16 +4623,16 @@
       <c r="C7" s="44">
         <v>8</v>
       </c>
-      <c r="D7" s="129"/>
-      <c r="E7" s="154"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="151"/>
       <c r="F7" s="82">
         <v>45</v>
       </c>
       <c r="G7" s="73">
         <v>17</v>
       </c>
-      <c r="H7" s="153"/>
-      <c r="I7" s="154"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="151"/>
       <c r="J7" s="82"/>
       <c r="K7" s="73"/>
       <c r="L7" s="82">
@@ -4650,7 +4641,7 @@
       <c r="M7" s="73">
         <v>19</v>
       </c>
-      <c r="N7" s="122">
+      <c r="N7" s="121">
         <f>F7+J7+L7</f>
         <v>88</v>
       </c>
@@ -4658,7 +4649,7 @@
         <f>COUNTIF(D7:L7,"&gt;30")</f>
         <v>2</v>
       </c>
-      <c r="P7" s="125"/>
+      <c r="P7" s="124"/>
       <c r="Q7" s="73">
         <v>2</v>
       </c>
@@ -4686,21 +4677,21 @@
       <c r="C8" s="44">
         <v>22</v>
       </c>
-      <c r="D8" s="129"/>
-      <c r="E8" s="154"/>
+      <c r="D8" s="150"/>
+      <c r="E8" s="151"/>
       <c r="F8" s="45">
         <v>59</v>
       </c>
       <c r="G8" s="73">
         <v>17</v>
       </c>
-      <c r="H8" s="153"/>
-      <c r="I8" s="154"/>
+      <c r="H8" s="150"/>
+      <c r="I8" s="151"/>
       <c r="J8" s="45"/>
       <c r="K8" s="73"/>
       <c r="L8" s="45"/>
       <c r="M8" s="73"/>
-      <c r="N8" s="122">
+      <c r="N8" s="121">
         <f>F8+J8+L8</f>
         <v>59</v>
       </c>
@@ -4708,7 +4699,7 @@
         <f>COUNTIF(D8:L8,"&gt;30")</f>
         <v>1</v>
       </c>
-      <c r="P8" s="125"/>
+      <c r="P8" s="124"/>
       <c r="Q8" s="73"/>
       <c r="R8" s="61">
         <f>SUMIF(G8:M8, "&lt;30")+P8+Q8</f>
@@ -4718,7 +4709,7 @@
         <f>R8/O8</f>
         <v>17</v>
       </c>
-      <c r="T8" s="173"/>
+      <c r="T8" s="127"/>
       <c r="U8" s="61"/>
       <c r="V8" s="61"/>
       <c r="W8" s="58"/>
@@ -4734,12 +4725,12 @@
       <c r="C9" s="44">
         <v>15</v>
       </c>
-      <c r="D9" s="129"/>
-      <c r="E9" s="154"/>
+      <c r="D9" s="150"/>
+      <c r="E9" s="151"/>
       <c r="F9" s="45"/>
       <c r="G9" s="73"/>
-      <c r="H9" s="153"/>
-      <c r="I9" s="154"/>
+      <c r="H9" s="150"/>
+      <c r="I9" s="151"/>
       <c r="J9" s="45">
         <v>52</v>
       </c>
@@ -4748,7 +4739,7 @@
       </c>
       <c r="L9" s="45"/>
       <c r="M9" s="73"/>
-      <c r="N9" s="122">
+      <c r="N9" s="121">
         <f>F9+J9+L9</f>
         <v>52</v>
       </c>
@@ -4756,7 +4747,7 @@
         <f>COUNTIF(D9:L9,"&gt;30")</f>
         <v>1</v>
       </c>
-      <c r="P9" s="125"/>
+      <c r="P9" s="124"/>
       <c r="Q9" s="73"/>
       <c r="R9" s="61">
         <f>SUMIF(G9:M9, "&lt;30")+P9+Q9</f>
@@ -4782,16 +4773,16 @@
       <c r="C10" s="44">
         <v>21</v>
       </c>
-      <c r="D10" s="129"/>
-      <c r="E10" s="154"/>
+      <c r="D10" s="150"/>
+      <c r="E10" s="151"/>
       <c r="F10" s="80">
         <v>61</v>
       </c>
       <c r="G10" s="73">
         <v>14</v>
       </c>
-      <c r="H10" s="153"/>
-      <c r="I10" s="154"/>
+      <c r="H10" s="150"/>
+      <c r="I10" s="151"/>
       <c r="J10" s="80">
         <v>56</v>
       </c>
@@ -4804,7 +4795,7 @@
       <c r="M10" s="73">
         <v>15</v>
       </c>
-      <c r="N10" s="122">
+      <c r="N10" s="121">
         <f>F10+J10+L10</f>
         <v>177</v>
       </c>
@@ -4812,7 +4803,7 @@
         <f>COUNTIF(D10:L10,"&gt;30")</f>
         <v>3</v>
       </c>
-      <c r="P10" s="125">
+      <c r="P10" s="124">
         <v>2</v>
       </c>
       <c r="Q10" s="73"/>
@@ -4840,21 +4831,21 @@
       <c r="C11" s="44">
         <v>18</v>
       </c>
-      <c r="D11" s="129"/>
-      <c r="E11" s="154"/>
+      <c r="D11" s="150"/>
+      <c r="E11" s="151"/>
       <c r="F11" s="45">
         <v>56</v>
       </c>
       <c r="G11" s="73">
         <v>16</v>
       </c>
-      <c r="H11" s="153"/>
-      <c r="I11" s="154"/>
+      <c r="H11" s="150"/>
+      <c r="I11" s="151"/>
       <c r="J11" s="45"/>
       <c r="K11" s="73"/>
       <c r="L11" s="45"/>
       <c r="M11" s="73"/>
-      <c r="N11" s="122">
+      <c r="N11" s="121">
         <f>F11+J11+L11</f>
         <v>56</v>
       </c>
@@ -4862,7 +4853,7 @@
         <f>COUNTIF(D11:L11,"&gt;30")</f>
         <v>1</v>
       </c>
-      <c r="P11" s="125"/>
+      <c r="P11" s="124"/>
       <c r="Q11" s="73"/>
       <c r="R11" s="61">
         <f>SUMIF(G11:M11, "&lt;30")+P11+Q11</f>
@@ -4888,21 +4879,21 @@
       <c r="C12" s="44">
         <v>8</v>
       </c>
-      <c r="D12" s="129"/>
-      <c r="E12" s="154"/>
+      <c r="D12" s="150"/>
+      <c r="E12" s="151"/>
       <c r="F12" s="45">
         <v>46</v>
       </c>
       <c r="G12" s="73">
         <v>16</v>
       </c>
-      <c r="H12" s="153"/>
-      <c r="I12" s="154"/>
+      <c r="H12" s="150"/>
+      <c r="I12" s="151"/>
       <c r="J12" s="45"/>
       <c r="K12" s="73"/>
       <c r="L12" s="45"/>
       <c r="M12" s="73"/>
-      <c r="N12" s="122">
+      <c r="N12" s="121">
         <f>F12+J12+L12</f>
         <v>46</v>
       </c>
@@ -4910,7 +4901,7 @@
         <f>COUNTIF(D12:L12,"&gt;30")</f>
         <v>1</v>
       </c>
-      <c r="P12" s="125"/>
+      <c r="P12" s="124"/>
       <c r="Q12" s="73"/>
       <c r="R12" s="61">
         <f>SUMIF(G12:M12, "&lt;30")+P12+Q12</f>
@@ -4936,16 +4927,16 @@
       <c r="C13" s="44">
         <v>17</v>
       </c>
-      <c r="D13" s="129"/>
-      <c r="E13" s="154"/>
+      <c r="D13" s="150"/>
+      <c r="E13" s="151"/>
       <c r="F13" s="45">
         <v>55</v>
       </c>
       <c r="G13" s="73">
         <v>16</v>
       </c>
-      <c r="H13" s="153"/>
-      <c r="I13" s="154"/>
+      <c r="H13" s="150"/>
+      <c r="I13" s="151"/>
       <c r="J13" s="45"/>
       <c r="K13" s="73"/>
       <c r="L13" s="45">
@@ -4954,7 +4945,7 @@
       <c r="M13" s="73">
         <v>15</v>
       </c>
-      <c r="N13" s="122">
+      <c r="N13" s="121">
         <f>F13+J13+L13</f>
         <v>111</v>
       </c>
@@ -4962,7 +4953,7 @@
         <f>COUNTIF(D13:L13,"&gt;30")</f>
         <v>2</v>
       </c>
-      <c r="P13" s="125"/>
+      <c r="P13" s="124"/>
       <c r="Q13" s="73"/>
       <c r="R13" s="61">
         <f>SUMIF(G13:M13, "&lt;30")+P13+Q13</f>
@@ -4980,34 +4971,41 @@
     </row>
     <row r="14" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="42" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="44">
-        <v>13</v>
-      </c>
-      <c r="D14" s="129"/>
-      <c r="E14" s="154"/>
-      <c r="F14" s="46"/>
+        <v>89</v>
+      </c>
+      <c r="C14" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="150"/>
+      <c r="E14" s="151"/>
+      <c r="F14" s="67"/>
       <c r="G14" s="73"/>
-      <c r="H14" s="153"/>
-      <c r="I14" s="154"/>
-      <c r="J14" s="46"/>
+      <c r="H14" s="150"/>
+      <c r="I14" s="151"/>
+      <c r="J14" s="67"/>
       <c r="K14" s="73"/>
-      <c r="L14" s="46"/>
+      <c r="L14" s="170">
+        <v>50</v>
+      </c>
       <c r="M14" s="73"/>
-      <c r="N14" s="122">
+      <c r="N14" s="121">
         <f>F14+J14+L14</f>
-        <v>0</v>
-      </c>
-      <c r="O14" s="58"/>
-      <c r="P14" s="125"/>
+        <v>50</v>
+      </c>
+      <c r="O14" s="58">
+        <f>COUNTIF(D14:L14,"&gt;30")</f>
+        <v>1</v>
+      </c>
+      <c r="P14" s="124">
+        <v>1</v>
+      </c>
       <c r="Q14" s="73"/>
       <c r="R14" s="61">
         <f>SUMIF(G14:M14, "&lt;30")+P14+Q14</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="85"/>
       <c r="T14" s="78"/>
@@ -5018,39 +5016,46 @@
     </row>
     <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="42" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="44">
+        <v>75</v>
+      </c>
+      <c r="C15" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="150"/>
+      <c r="E15" s="151"/>
+      <c r="F15" s="45">
+        <v>46</v>
+      </c>
+      <c r="G15" s="73"/>
+      <c r="H15" s="150"/>
+      <c r="I15" s="151"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="45">
+        <v>46</v>
+      </c>
+      <c r="M15" s="73"/>
+      <c r="N15" s="121">
+        <f>F15+J15+L15</f>
+        <v>92</v>
+      </c>
+      <c r="O15" s="58">
+        <f>COUNTIF(D15:L15,"&gt;30")</f>
         <v>2</v>
       </c>
-      <c r="D15" s="129"/>
-      <c r="E15" s="154"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="73"/>
-      <c r="H15" s="153"/>
-      <c r="I15" s="154"/>
-      <c r="J15" s="67"/>
-      <c r="K15" s="73"/>
-      <c r="L15" s="67"/>
-      <c r="M15" s="73"/>
-      <c r="N15" s="122">
-        <f>F15+J15+L15</f>
-        <v>0</v>
-      </c>
-      <c r="O15" s="58"/>
       <c r="P15" s="125"/>
-      <c r="Q15" s="73"/>
+      <c r="Q15" s="83"/>
       <c r="R15" s="61">
         <f>SUMIF(G15:M15, "&lt;30")+P15+Q15</f>
         <v>0</v>
       </c>
       <c r="S15" s="85"/>
-      <c r="T15" s="78"/>
-      <c r="U15" s="61"/>
-      <c r="V15" s="61"/>
+      <c r="T15" s="79"/>
+      <c r="U15" s="58"/>
+      <c r="V15" s="58"/>
       <c r="W15" s="58"/>
       <c r="X15" s="64"/>
     </row>
@@ -5064,19 +5069,19 @@
       <c r="C16" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="129"/>
-      <c r="E16" s="154"/>
+      <c r="D16" s="150"/>
+      <c r="E16" s="151"/>
       <c r="F16" s="45">
         <v>51</v>
       </c>
       <c r="G16" s="73"/>
-      <c r="H16" s="153"/>
-      <c r="I16" s="154"/>
+      <c r="H16" s="150"/>
+      <c r="I16" s="151"/>
       <c r="J16" s="45"/>
       <c r="K16" s="73"/>
       <c r="L16" s="45"/>
       <c r="M16" s="73"/>
-      <c r="N16" s="122">
+      <c r="N16" s="121">
         <f>F16+J16+L16</f>
         <v>51</v>
       </c>
@@ -5084,7 +5089,7 @@
         <f>COUNTIF(D16:L16,"&gt;30")</f>
         <v>1</v>
       </c>
-      <c r="P16" s="125"/>
+      <c r="P16" s="124"/>
       <c r="Q16" s="73"/>
       <c r="R16" s="61">
         <f>SUMIF(G16:M16, "&lt;30")+P16+Q16</f>
@@ -5099,42 +5104,42 @@
     </row>
     <row r="17" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="42" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="C17" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="129"/>
-      <c r="E17" s="154"/>
-      <c r="F17" s="67"/>
+      <c r="D17" s="150"/>
+      <c r="E17" s="151"/>
+      <c r="F17" s="45">
+        <v>41</v>
+      </c>
       <c r="G17" s="73"/>
-      <c r="H17" s="153"/>
-      <c r="I17" s="154"/>
-      <c r="J17" s="67"/>
+      <c r="H17" s="150"/>
+      <c r="I17" s="151"/>
+      <c r="J17" s="45"/>
       <c r="K17" s="73"/>
-      <c r="L17" s="120">
-        <v>50</v>
-      </c>
+      <c r="L17" s="45"/>
       <c r="M17" s="73"/>
-      <c r="N17" s="122">
+      <c r="N17" s="121">
         <f>F17+J17+L17</f>
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="O17" s="58">
         <f>COUNTIF(D17:L17,"&gt;30")</f>
         <v>1</v>
       </c>
-      <c r="P17" s="125"/>
+      <c r="P17" s="124"/>
       <c r="Q17" s="73"/>
       <c r="R17" s="61">
         <f>SUMIF(G17:M17, "&lt;30")+P17+Q17</f>
         <v>0</v>
       </c>
       <c r="S17" s="85"/>
-      <c r="T17" s="78"/>
+      <c r="T17" s="79"/>
       <c r="U17" s="61"/>
       <c r="V17" s="61"/>
       <c r="W17" s="58"/>
@@ -5142,87 +5147,75 @@
     </row>
     <row r="18" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="42" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="129"/>
-      <c r="E18" s="154"/>
-      <c r="F18" s="45">
-        <v>46</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="C18" s="44">
+        <v>13</v>
+      </c>
+      <c r="D18" s="150"/>
+      <c r="E18" s="151"/>
+      <c r="F18" s="46"/>
       <c r="G18" s="73"/>
-      <c r="H18" s="153"/>
-      <c r="I18" s="154"/>
-      <c r="J18" s="45"/>
+      <c r="H18" s="150"/>
+      <c r="I18" s="151"/>
+      <c r="J18" s="46"/>
       <c r="K18" s="73"/>
-      <c r="L18" s="45">
-        <v>46</v>
-      </c>
+      <c r="L18" s="46"/>
       <c r="M18" s="73"/>
-      <c r="N18" s="122">
+      <c r="N18" s="121">
         <f>F18+J18+L18</f>
-        <v>92</v>
-      </c>
-      <c r="O18" s="58">
-        <f>COUNTIF(D18:L18,"&gt;30")</f>
-        <v>2</v>
-      </c>
-      <c r="P18" s="126"/>
-      <c r="Q18" s="83"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="58"/>
+      <c r="P18" s="124"/>
+      <c r="Q18" s="73"/>
       <c r="R18" s="61">
         <f>SUMIF(G18:M18, "&lt;30")+P18+Q18</f>
         <v>0</v>
       </c>
       <c r="S18" s="85"/>
-      <c r="T18" s="79"/>
-      <c r="U18" s="58"/>
-      <c r="V18" s="58"/>
+      <c r="T18" s="78"/>
+      <c r="U18" s="61"/>
+      <c r="V18" s="61"/>
       <c r="W18" s="58"/>
       <c r="X18" s="64"/>
     </row>
     <row r="19" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="42" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="129"/>
-      <c r="E19" s="154"/>
-      <c r="F19" s="45">
-        <v>41</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C19" s="44">
+        <v>2</v>
+      </c>
+      <c r="D19" s="150"/>
+      <c r="E19" s="151"/>
+      <c r="F19" s="67"/>
       <c r="G19" s="73"/>
-      <c r="H19" s="153"/>
-      <c r="I19" s="154"/>
-      <c r="J19" s="45"/>
+      <c r="H19" s="150"/>
+      <c r="I19" s="151"/>
+      <c r="J19" s="67"/>
       <c r="K19" s="73"/>
-      <c r="L19" s="45"/>
+      <c r="L19" s="67"/>
       <c r="M19" s="73"/>
-      <c r="N19" s="122">
+      <c r="N19" s="121">
         <f>F19+J19+L19</f>
-        <v>41</v>
-      </c>
-      <c r="O19" s="58">
-        <f>COUNTIF(D19:L19,"&gt;30")</f>
-        <v>1</v>
-      </c>
-      <c r="P19" s="125"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="58"/>
+      <c r="P19" s="124"/>
       <c r="Q19" s="73"/>
       <c r="R19" s="61">
         <f>SUMIF(G19:M19, "&lt;30")+P19+Q19</f>
         <v>0</v>
       </c>
       <c r="S19" s="85"/>
-      <c r="T19" s="79"/>
+      <c r="T19" s="78"/>
       <c r="U19" s="61"/>
       <c r="V19" s="61"/>
       <c r="W19" s="58"/>
@@ -5238,22 +5231,22 @@
       <c r="C20" s="44">
         <v>15</v>
       </c>
-      <c r="D20" s="129"/>
-      <c r="E20" s="154"/>
+      <c r="D20" s="150"/>
+      <c r="E20" s="151"/>
       <c r="F20" s="45"/>
       <c r="G20" s="73"/>
-      <c r="H20" s="153"/>
-      <c r="I20" s="154"/>
+      <c r="H20" s="150"/>
+      <c r="I20" s="151"/>
       <c r="J20" s="45"/>
       <c r="K20" s="73"/>
       <c r="L20" s="45"/>
       <c r="M20" s="73"/>
-      <c r="N20" s="122">
+      <c r="N20" s="121">
         <f>F20+J20+L20</f>
         <v>0</v>
       </c>
       <c r="O20" s="58"/>
-      <c r="P20" s="125"/>
+      <c r="P20" s="124"/>
       <c r="Q20" s="73"/>
       <c r="R20" s="61">
         <f>SUMIF(G20:M20, "&lt;30")+P20+Q20</f>
@@ -5276,19 +5269,19 @@
       <c r="C21" s="71">
         <v>11</v>
       </c>
-      <c r="D21" s="130"/>
-      <c r="E21" s="156"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="153"/>
       <c r="F21" s="52"/>
       <c r="G21" s="74"/>
-      <c r="H21" s="155"/>
-      <c r="I21" s="156"/>
+      <c r="H21" s="152"/>
+      <c r="I21" s="153"/>
       <c r="J21" s="52"/>
       <c r="K21" s="74"/>
       <c r="L21" s="52"/>
       <c r="M21" s="74"/>
-      <c r="N21" s="123"/>
+      <c r="N21" s="122"/>
       <c r="O21" s="59"/>
-      <c r="P21" s="127"/>
+      <c r="P21" s="126"/>
       <c r="Q21" s="74"/>
       <c r="R21" s="62">
         <f>SUMIF(G21:M21, "&lt;30")+P21+Q21</f>
@@ -5380,20 +5373,13 @@
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:X21">
     <sortCondition descending="1" ref="S4:S21"/>
+    <sortCondition descending="1" ref="R4:R21"/>
+    <sortCondition descending="1" ref="N4:N21"/>
     <sortCondition ref="B4:B21"/>
   </sortState>
   <mergeCells count="27">
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="N1:N3"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="D4:E21"/>
     <mergeCell ref="H4:I21"/>
-    <mergeCell ref="E4:E21"/>
     <mergeCell ref="A1:B3"/>
     <mergeCell ref="C1:C3"/>
     <mergeCell ref="F1:G1"/>
@@ -5410,6 +5396,15 @@
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="N1:N3"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="Q2:Q3"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5437,23 +5432,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
@@ -5467,23 +5462,23 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="133" t="s">
+      <c r="A2" s="130" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -6387,23 +6382,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
@@ -6417,23 +6412,23 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="133" t="s">
+      <c r="A2" s="130" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -7976,23 +7971,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
@@ -8006,23 +8001,23 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="133" t="s">
+      <c r="A2" s="130" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -8926,23 +8921,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="17" x14ac:dyDescent="0.3">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="167" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-      <c r="H1" s="171"/>
-      <c r="I1" s="171"/>
-      <c r="J1" s="171"/>
-      <c r="K1" s="171"/>
-      <c r="L1" s="171"/>
-      <c r="M1" s="171"/>
-      <c r="N1" s="171"/>
-      <c r="O1" s="171"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="168"/>
+      <c r="H1" s="168"/>
+      <c r="I1" s="168"/>
+      <c r="J1" s="168"/>
+      <c r="K1" s="168"/>
+      <c r="L1" s="168"/>
+      <c r="M1" s="168"/>
+      <c r="N1" s="168"/>
+      <c r="O1" s="168"/>
       <c r="P1" s="96"/>
       <c r="Q1" s="96"/>
       <c r="R1" s="96"/>
@@ -8956,23 +8951,23 @@
       <c r="Z1" s="96"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="172" t="s">
+      <c r="A2" s="169" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="171"/>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="171"/>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="171"/>
-      <c r="J2" s="171"/>
-      <c r="K2" s="171"/>
-      <c r="L2" s="171"/>
-      <c r="M2" s="171"/>
-      <c r="N2" s="171"/>
-      <c r="O2" s="171"/>
+      <c r="B2" s="168"/>
+      <c r="C2" s="168"/>
+      <c r="D2" s="168"/>
+      <c r="E2" s="168"/>
+      <c r="F2" s="168"/>
+      <c r="G2" s="168"/>
+      <c r="H2" s="168"/>
+      <c r="I2" s="168"/>
+      <c r="J2" s="168"/>
+      <c r="K2" s="168"/>
+      <c r="L2" s="168"/>
+      <c r="M2" s="168"/>
+      <c r="N2" s="168"/>
+      <c r="O2" s="168"/>
       <c r="P2" s="96"/>
       <c r="Q2" s="96"/>
       <c r="R2" s="96"/>
@@ -9438,23 +9433,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
@@ -9468,23 +9463,23 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="133" t="s">
+      <c r="A2" s="130" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
